--- a/output/topology_excel/11790.xlsx
+++ b/output/topology_excel/11790.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="n">
         <v>3</v>
-      </c>
-      <c r="B17" t="n">
-        <v>18</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="n">
         <v>14</v>
-      </c>
-      <c r="B18" t="n">
-        <v>17</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B20" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B21" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F21" t="n">
         <v>12</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>163</v>
+        <v>74</v>
       </c>
       <c r="F22" t="n">
         <v>12</v>
@@ -924,10 +924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B24" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B25" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,40 +982,40 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,29 +1026,29 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="F27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="F28" t="n">
         <v>13</v>
@@ -1056,24 +1056,24 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="F29" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
@@ -1081,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="F30" t="n">
         <v>12</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,19 +1114,19 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="F31" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="n">
         <v>2</v>
       </c>
-      <c r="B32" t="n">
-        <v>5</v>
-      </c>
       <c r="C32" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="F32" t="n">
         <v>12</v>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="F33" t="n">
         <v>12</v>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,18 +1180,18 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>206</v>
+        <v>289</v>
       </c>
       <c r="F34" t="n">
-        <v>203</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,18 +1202,18 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>171</v>
+        <v>116</v>
       </c>
       <c r="F35" t="n">
-        <v>140</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,19 +1224,19 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" t="n">
         <v>3</v>
       </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
       <c r="C37" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1246,18 +1246,18 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>166</v>
+        <v>451</v>
       </c>
       <c r="F37" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B38" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,18 +1268,18 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>232</v>
+        <v>108</v>
       </c>
       <c r="F38" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>451</v>
+        <v>170</v>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40">
@@ -1301,7 +1301,7 @@
         <v>4</v>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>102</v>
+        <v>295</v>
       </c>
       <c r="F40" t="n">
         <v>12</v>
@@ -1323,7 +1323,7 @@
         <v>5</v>
       </c>
       <c r="B41" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,10 +1334,10 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F41" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42">
@@ -1345,7 +1345,7 @@
         <v>5</v>
       </c>
       <c r="B42" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,10 +1356,10 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="F42" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
@@ -1367,7 +1367,7 @@
         <v>5</v>
       </c>
       <c r="B43" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>133</v>
+        <v>317</v>
       </c>
       <c r="F43" t="n">
         <v>12</v>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>149</v>
+        <v>206</v>
       </c>
       <c r="F44" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
@@ -1411,7 +1411,7 @@
         <v>6</v>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="F45" t="n">
         <v>12</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B46" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,18 +1444,18 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>56</v>
+        <v>170</v>
       </c>
       <c r="F46" t="n">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B47" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>336</v>
+        <v>109</v>
       </c>
       <c r="F47" t="n">
         <v>12</v>
@@ -1477,7 +1477,7 @@
         <v>7</v>
       </c>
       <c r="B48" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="F48" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49">
@@ -1499,7 +1499,7 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>133</v>
+        <v>336</v>
       </c>
       <c r="F49" t="n">
         <v>12</v>
@@ -1518,10 +1518,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,18 +1532,18 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="F50" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B51" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1554,18 +1554,18 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="F51" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B52" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1576,18 +1576,18 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>85</v>
+        <v>289</v>
       </c>
       <c r="F52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B53" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>214</v>
+        <v>63</v>
       </c>
       <c r="F53" t="n">
         <v>12</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B54" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,18 +1620,18 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="F54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B55" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="F55" t="n">
         <v>12</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1664,18 +1664,18 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="F56" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B57" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1686,18 +1686,18 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>397</v>
+        <v>133</v>
       </c>
       <c r="F57" t="n">
-        <v>71</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B58" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1708,18 +1708,18 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="F58" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B59" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1730,18 +1730,18 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="F59" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B60" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1752,18 +1752,18 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>335</v>
+        <v>44</v>
       </c>
       <c r="F60" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B61" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1774,18 +1774,18 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>364</v>
+        <v>162</v>
       </c>
       <c r="F61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B62" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1796,18 +1796,18 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>444</v>
+        <v>228</v>
       </c>
       <c r="F62" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B63" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1818,18 +1818,18 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>303</v>
+        <v>149</v>
       </c>
       <c r="F63" t="n">
-        <v>253</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B64" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="F64" t="n">
         <v>12</v>
@@ -1848,7 +1848,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B65" t="n">
         <v>23</v>
@@ -1862,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="F65" t="n">
         <v>12</v>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B66" t="n">
         <v>24</v>
@@ -1884,18 +1884,18 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>225</v>
+        <v>149</v>
       </c>
       <c r="F66" t="n">
-        <v>69</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B67" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1906,18 +1906,18 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>262</v>
+        <v>133</v>
       </c>
       <c r="F67" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B68" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F68" t="n">
         <v>11</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B69" t="n">
         <v>27</v>
@@ -1950,18 +1950,18 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="F69" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B70" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>214</v>
+        <v>86</v>
       </c>
       <c r="F70" t="n">
         <v>12</v>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B71" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1994,18 +1994,18 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="F71" t="n">
-        <v>11</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B72" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2016,32 +2016,472 @@
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>187</v>
+        <v>102</v>
       </c>
       <c r="F72" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B73" t="n">
+        <v>32</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>203</v>
+      </c>
+      <c r="F73" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>16</v>
+      </c>
+      <c r="B74" t="n">
+        <v>25</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>193</v>
+      </c>
+      <c r="F74" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>16</v>
+      </c>
+      <c r="B75" t="n">
         <v>27</v>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="n">
-        <v>228</v>
-      </c>
-      <c r="F73" t="n">
-        <v>12</v>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>364</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>16</v>
+      </c>
+      <c r="B76" t="n">
+        <v>28</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>180</v>
+      </c>
+      <c r="F76" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>17</v>
+      </c>
+      <c r="B77" t="n">
+        <v>18</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>102</v>
+      </c>
+      <c r="F77" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>18</v>
+      </c>
+      <c r="B78" t="n">
+        <v>22</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>133</v>
+      </c>
+      <c r="F78" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>19</v>
+      </c>
+      <c r="B79" t="n">
+        <v>20</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>159</v>
+      </c>
+      <c r="F79" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>20</v>
+      </c>
+      <c r="B80" t="n">
+        <v>21</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>83</v>
+      </c>
+      <c r="F80" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>22</v>
+      </c>
+      <c r="B81" t="n">
+        <v>24</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>151</v>
+      </c>
+      <c r="F81" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>23</v>
+      </c>
+      <c r="B82" t="n">
+        <v>24</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>133</v>
+      </c>
+      <c r="F82" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>25</v>
+      </c>
+      <c r="B83" t="n">
+        <v>28</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>264</v>
+      </c>
+      <c r="F83" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>27</v>
+      </c>
+      <c r="B84" t="n">
+        <v>28</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>245</v>
+      </c>
+      <c r="F84" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>27</v>
+      </c>
+      <c r="B85" t="n">
+        <v>29</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>119</v>
+      </c>
+      <c r="F85" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>28</v>
+      </c>
+      <c r="B86" t="n">
+        <v>31</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>160</v>
+      </c>
+      <c r="F86" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>29</v>
+      </c>
+      <c r="B87" t="n">
+        <v>30</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>214</v>
+      </c>
+      <c r="F87" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>31</v>
+      </c>
+      <c r="B88" t="n">
+        <v>32</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>187</v>
+      </c>
+      <c r="F88" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2</v>
+      </c>
+      <c r="B89" t="n">
+        <v>6</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>106</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2</v>
+      </c>
+      <c r="B90" t="n">
+        <v>20</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>166</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>9</v>
+      </c>
+      <c r="B91" t="n">
+        <v>24</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>31</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>16</v>
+      </c>
+      <c r="B92" t="n">
+        <v>25</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>87</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>15</v>
+      </c>
+      <c r="B93" t="n">
+        <v>28</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>302</v>
+      </c>
+      <c r="F93" t="n">
+        <v>295</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/11790.xlsx
+++ b/output/topology_excel/11790.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>12</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>12</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>12</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>12</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>12</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>12</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>12</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>12</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>11</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>12</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>12</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>11</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>12</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +803,8 @@
       <c r="F15" t="n">
         <v>12</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +827,8 @@
       <c r="F16" t="n">
         <v>12</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +851,8 @@
       <c r="F17" t="n">
         <v>8</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +875,8 @@
       <c r="F18" t="n">
         <v>12</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +899,8 @@
       <c r="F19" t="n">
         <v>13</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +923,8 @@
       <c r="F20" t="n">
         <v>10</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +947,8 @@
       <c r="F21" t="n">
         <v>12</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +971,8 @@
       <c r="F22" t="n">
         <v>12</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +995,8 @@
       <c r="F23" t="n">
         <v>12</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1019,8 @@
       <c r="F24" t="n">
         <v>11</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1043,8 @@
       <c r="F25" t="n">
         <v>11</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1067,8 @@
       <c r="F26" t="n">
         <v>12</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1091,8 @@
       <c r="F27" t="n">
         <v>13</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1115,8 @@
       <c r="F28" t="n">
         <v>13</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1139,8 @@
       <c r="F29" t="n">
         <v>12</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1163,8 @@
       <c r="F30" t="n">
         <v>12</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1187,8 @@
       <c r="F31" t="n">
         <v>12</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1211,8 @@
       <c r="F32" t="n">
         <v>12</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1235,8 @@
       <c r="F33" t="n">
         <v>12</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1177,13 +1251,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>289</v>
+        <v>162</v>
       </c>
       <c r="F34" t="n">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="G34" t="n">
+        <v>21</v>
+      </c>
+      <c r="H34" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="35">
@@ -1207,6 +1287,8 @@
       <c r="F35" t="n">
         <v>12</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1227,8 +1309,10 @@
         <v>135</v>
       </c>
       <c r="F36" t="n">
-        <v>52</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1335,8 @@
       <c r="F37" t="n">
         <v>8</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1359,8 @@
       <c r="F38" t="n">
         <v>13</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1287,13 +1375,19 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>170</v>
+        <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>60</v>
+        <v>12</v>
+      </c>
+      <c r="G39" t="n">
+        <v>158</v>
+      </c>
+      <c r="H39" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="40">
@@ -1317,6 +1411,8 @@
       <c r="F40" t="n">
         <v>12</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1331,13 +1427,19 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>164</v>
+        <v>41</v>
       </c>
       <c r="F41" t="n">
-        <v>53</v>
+        <v>12</v>
+      </c>
+      <c r="G41" t="n">
+        <v>152</v>
+      </c>
+      <c r="H41" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="42">
@@ -1361,6 +1463,8 @@
       <c r="F42" t="n">
         <v>12</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1487,8 @@
       <c r="F43" t="n">
         <v>12</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1397,13 +1503,19 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="F44" t="n">
-        <v>23</v>
+        <v>12</v>
+      </c>
+      <c r="G44" t="n">
+        <v>12</v>
+      </c>
+      <c r="H44" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="45">
@@ -1427,6 +1539,8 @@
       <c r="F45" t="n">
         <v>12</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1441,13 +1555,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="F46" t="n">
-        <v>87</v>
+        <v>12</v>
+      </c>
+      <c r="G46" t="n">
+        <v>75</v>
+      </c>
+      <c r="H46" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="47">
@@ -1471,6 +1591,8 @@
       <c r="F47" t="n">
         <v>12</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1615,8 @@
       <c r="F48" t="n">
         <v>26</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1515,6 +1639,8 @@
       <c r="F49" t="n">
         <v>12</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1529,13 +1655,19 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="F50" t="n">
-        <v>55</v>
+        <v>12</v>
+      </c>
+      <c r="G50" t="n">
+        <v>43</v>
+      </c>
+      <c r="H50" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="51">
@@ -1551,13 +1683,19 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="F51" t="n">
-        <v>58</v>
+        <v>12</v>
+      </c>
+      <c r="G51" t="n">
+        <v>46</v>
+      </c>
+      <c r="H51" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="52">
@@ -1581,6 +1719,8 @@
       <c r="F52" t="n">
         <v>13</v>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1603,6 +1743,8 @@
       <c r="F53" t="n">
         <v>12</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1625,6 +1767,8 @@
       <c r="F54" t="n">
         <v>13</v>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1647,6 +1791,8 @@
       <c r="F55" t="n">
         <v>12</v>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1661,13 +1807,19 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="F56" t="n">
-        <v>40</v>
+        <v>12</v>
+      </c>
+      <c r="G56" t="n">
+        <v>50</v>
+      </c>
+      <c r="H56" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="57">
@@ -1691,6 +1843,8 @@
       <c r="F57" t="n">
         <v>12</v>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1705,13 +1859,19 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="F58" t="n">
-        <v>120</v>
+        <v>12</v>
+      </c>
+      <c r="G58" t="n">
+        <v>108</v>
+      </c>
+      <c r="H58" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="59">
@@ -1735,6 +1895,8 @@
       <c r="F59" t="n">
         <v>26</v>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1757,6 +1919,8 @@
       <c r="F60" t="n">
         <v>11</v>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1779,6 +1943,8 @@
       <c r="F61" t="n">
         <v>11</v>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1801,6 +1967,8 @@
       <c r="F62" t="n">
         <v>12</v>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1823,6 +1991,8 @@
       <c r="F63" t="n">
         <v>12</v>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1845,6 +2015,8 @@
       <c r="F64" t="n">
         <v>12</v>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1867,6 +2039,8 @@
       <c r="F65" t="n">
         <v>12</v>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1889,6 +2063,8 @@
       <c r="F66" t="n">
         <v>12</v>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1911,6 +2087,8 @@
       <c r="F67" t="n">
         <v>12</v>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1933,6 +2111,8 @@
       <c r="F68" t="n">
         <v>11</v>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1953,8 +2133,10 @@
         <v>233</v>
       </c>
       <c r="F69" t="n">
-        <v>58</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1977,6 +2159,8 @@
       <c r="F70" t="n">
         <v>12</v>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1991,13 +2175,19 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>225</v>
+        <v>57</v>
       </c>
       <c r="F71" t="n">
-        <v>69</v>
+        <v>11</v>
+      </c>
+      <c r="G71" t="n">
+        <v>214</v>
+      </c>
+      <c r="H71" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="72">
@@ -2013,13 +2203,19 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F72" t="n">
-        <v>55</v>
+        <v>11</v>
+      </c>
+      <c r="G72" t="n">
+        <v>44</v>
+      </c>
+      <c r="H72" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="73">
@@ -2043,6 +2239,8 @@
       <c r="F73" t="n">
         <v>11</v>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2065,6 +2263,8 @@
       <c r="F74" t="n">
         <v>12</v>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2087,6 +2287,8 @@
       <c r="F75" t="n">
         <v>10</v>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2109,6 +2311,8 @@
       <c r="F76" t="n">
         <v>18</v>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2131,6 +2335,8 @@
       <c r="F77" t="n">
         <v>12</v>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2153,6 +2359,8 @@
       <c r="F78" t="n">
         <v>12</v>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2175,6 +2383,8 @@
       <c r="F79" t="n">
         <v>12</v>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2197,6 +2407,8 @@
       <c r="F80" t="n">
         <v>11</v>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2219,6 +2431,8 @@
       <c r="F81" t="n">
         <v>12</v>
       </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2233,13 +2447,19 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="F82" t="n">
-        <v>56</v>
+        <v>12</v>
+      </c>
+      <c r="G82" t="n">
+        <v>121</v>
+      </c>
+      <c r="H82" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="83">
@@ -2263,6 +2483,8 @@
       <c r="F83" t="n">
         <v>18</v>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2285,6 +2507,8 @@
       <c r="F84" t="n">
         <v>20</v>
       </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2307,6 +2531,8 @@
       <c r="F85" t="n">
         <v>12</v>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2321,13 +2547,19 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
       <c r="F86" t="n">
-        <v>52</v>
+        <v>11</v>
+      </c>
+      <c r="G86" t="n">
+        <v>149</v>
+      </c>
+      <c r="H86" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="87">
@@ -2351,6 +2583,8 @@
       <c r="F87" t="n">
         <v>12</v>
       </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2373,6 +2607,8 @@
       <c r="F88" t="n">
         <v>11</v>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2395,6 +2631,8 @@
       <c r="F89" t="n">
         <v>1</v>
       </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2417,6 +2655,8 @@
       <c r="F90" t="n">
         <v>1</v>
       </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2439,6 +2679,8 @@
       <c r="F91" t="n">
         <v>1</v>
       </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2461,6 +2703,8 @@
       <c r="F92" t="n">
         <v>1</v>
       </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2483,6 +2727,8 @@
       <c r="F93" t="n">
         <v>295</v>
       </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
